--- a/xlTest.xlsx
+++ b/xlTest.xlsx
@@ -1,22 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\root\dev\savine_scripting\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E34F643-E9EC-4DE7-A2F8-89660502CDCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="120" windowWidth="28755" windowHeight="13095"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scripts" sheetId="5" r:id="rId1"/>
     <sheet name="Sharp" sheetId="1" r:id="rId2"/>
     <sheet name="Fuzzy" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="125725" calcMode="manual" calcCompleted="0" calcOnSave="0"/>
+  <calcPr calcId="191029" calcMode="manual" calcCompleted="0" calcOnSave="0"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="39">
   <si>
     <t>Today</t>
   </si>
@@ -84,36 +103,66 @@
     <t>Num Sim</t>
   </si>
   <si>
-    <t>opt pays max( 0, spot() - 100 )</t>
-  </si>
-  <si>
     <t>Value</t>
   </si>
   <si>
-    <t>Other scripts (copy and paste from here)</t>
-  </si>
-  <si>
-    <t>call</t>
-  </si>
-  <si>
-    <t>barrier</t>
-  </si>
-  <si>
-    <t>strike</t>
-  </si>
-  <si>
-    <t>autocall</t>
+    <t>VAR_1 = 7 - 3 - 4</t>
+  </si>
+  <si>
+    <t>IF VAR_1 = 0 THEN VAR_2 = 7 - 3 - 4 ENDIF</t>
+  </si>
+  <si>
+    <t>VAR_3 = 2 ^ 3 ^ 4</t>
+  </si>
+  <si>
+    <t>VAR_4 = -2 ^ 2</t>
+  </si>
+  <si>
+    <t>Example scripts below</t>
+  </si>
+  <si>
+    <t>ALIVE = 1</t>
+  </si>
+  <si>
+    <t>IF SPOT() &gt; 110 THEN ALIVE = 0 ENDIF</t>
+  </si>
+  <si>
+    <t>RKO PAYS ALIVE * MAX( SPOT() - 100, 0)</t>
+  </si>
+  <si>
+    <t>IF SPOT() &gt; 100 THEN AUTOCALL PAYS 110 ALIVE = 0 ENDIF</t>
+  </si>
+  <si>
+    <t>IF SPOT() &gt; 100 THEN AUTOCALL PAYS ALIVE * 120 ALIVE = 0 ENDIF</t>
+  </si>
+  <si>
+    <t>IF SPOT() &gt; 100 THEN AUTOCALL PAYS ALIVE * 130 ELSE AUTOCALL PAYS ALIVE * 50 ENDIF</t>
+  </si>
+  <si>
+    <t>OPT PAYS MAX( 0, SPOT() - 100 )</t>
+  </si>
+  <si>
+    <t>Call, strike = 100</t>
+  </si>
+  <si>
+    <t>Monthly monitored barrier @ 110, up and out call, strike = 100</t>
+  </si>
+  <si>
+    <t>Autocallable</t>
+  </si>
+  <si>
+    <t>Just testing expressions</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,8 +206,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -178,6 +235,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -213,11 +276,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -226,13 +288,49 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="3"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" fontId="5" fillId="4" borderId="0" xfId="5" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="5" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="5" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -244,17 +342,37 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -307,34 +425,34 @@
             <c:numRef>
               <c:f>Sharp!$C$24:$C$33</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"??_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>90.223999999997403</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>90.457999999982079</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>90.362999999973212</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>90.220750000007257</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>90.160200000033896</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>90.35516666665481</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>90.347142857107599</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>90.409624999958481</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>90.3547777778181</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>90.23189999997507</c:v>
@@ -342,12 +460,27 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-367F-43D5-895D-2DD87B900139}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:axId val="199673728"/>
         <c:axId val="199675264"/>
       </c:scatterChart>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
@@ -400,22 +533,22 @@
             <c:numRef>
               <c:f>Sharp!$E$24:$E$33</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"??_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.0000000000238742</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-9.9999999999056399</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-17.500000000012506</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-24.000000000086175</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -424,18 +557,32 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-17.500000000012506</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-15.55555555569299</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-19.99999999981128</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-367F-43D5-895D-2DD87B900139}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:axId val="199682688"/>
         <c:axId val="199681152"/>
       </c:scatterChart>
@@ -444,8 +591,11 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="low"/>
         <c:crossAx val="199675264"/>
         <c:crosses val="autoZero"/>
@@ -456,6 +606,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
@@ -464,7 +615,9 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-" sourceLinked="1"/>
+        <c:numFmt formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="199673728"/>
         <c:crosses val="autoZero"/>
@@ -475,8 +628,11 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="r"/>
-        <c:numFmt formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-" sourceLinked="1"/>
+        <c:numFmt formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="199682688"/>
         <c:crosses val="max"/>
@@ -490,6 +646,8 @@
         <c:delete val="1"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
         <c:crossAx val="199681152"/>
         <c:crosses val="autoZero"/>
@@ -498,9 +656,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -511,13 +671,25 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -570,41 +742,47 @@
             <c:numRef>
               <c:f>Fuzzy!$C$24:$C$33</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"??_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>89.699999999997587</c:v>
+                  <c:v>90.223999999997403</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>90.056999999981969</c:v>
+                  <c:v>90.457999999982079</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>90.071999999973059</c:v>
+                  <c:v>90.362999999973212</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>90.558000000007993</c:v>
+                  <c:v>90.220750000007257</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>90.196400000035112</c:v>
+                  <c:v>90.160200000033896</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>90.404666666654421</c:v>
+                  <c:v>90.35516666665481</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>90.30714285710927</c:v>
+                  <c:v>90.347142857107599</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>90.392749999958625</c:v>
+                  <c:v>90.409624999958481</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>90.341333333373967</c:v>
+                  <c:v>90.3547777778181</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>90.409299999973271</c:v>
+                  <c:v>90.23189999997507</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1B73-4ADE-AB62-1C2ABDB5F84D}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -658,47 +836,62 @@
             <c:numRef>
               <c:f>Fuzzy!$F$24:$F$33</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"??_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>89.699999999997587</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>90.056999999981969</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>90.071999999973059</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>90.558000000007993</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>90.196400000035112</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>90.404666666654421</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>90.30714285710927</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>90.392749999958625</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>90.341333333373967</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>90.409299999973271</c:v>
+                  <c:v>90.23189999997507</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1B73-4ADE-AB62-1C2ABDB5F84D}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:axId val="200234880"/>
         <c:axId val="200236416"/>
       </c:scatterChart>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
@@ -751,7 +944,7 @@
             <c:numRef>
               <c:f>Fuzzy!$E$24:$E$33</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"??_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -760,25 +953,25 @@
                   <c:v>5.0000000000238742</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>-9.9999999999056399</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-27.500000000060254</c:v>
+                  <c:v>-17.500000000012506</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-30.000000000001137</c:v>
+                  <c:v>-24.000000000086175</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.33333333330188</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-11.428571428666601</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.2499999999704414</c:v>
+                  <c:v>-17.500000000012506</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-23.333333333255268</c:v>
+                  <c:v>-15.55555555569299</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>-19.99999999981128</c:v>
@@ -786,6 +979,12 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1B73-4ADE-AB62-1C2ABDB5F84D}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -839,42 +1038,56 @@
             <c:numRef>
               <c:f>Fuzzy!$G$24:$G$33</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"??_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.0000000000238742</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-27.500000000060254</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-30.000000000001137</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.33333333330188</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-11.428571428666601</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.2499999999704414</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-23.333333333255268</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-19.99999999981128</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-1B73-4ADE-AB62-1C2ABDB5F84D}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:axId val="200243840"/>
         <c:axId val="200242304"/>
       </c:scatterChart>
@@ -883,8 +1096,11 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="low"/>
         <c:crossAx val="200236416"/>
         <c:crosses val="autoZero"/>
@@ -895,6 +1111,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
@@ -903,7 +1120,9 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-" sourceLinked="1"/>
+        <c:numFmt formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="200234880"/>
         <c:crosses val="autoZero"/>
@@ -914,8 +1133,11 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="r"/>
-        <c:numFmt formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-" sourceLinked="1"/>
+        <c:numFmt formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="200243840"/>
         <c:crosses val="max"/>
@@ -929,6 +1151,8 @@
         <c:delete val="1"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
         <c:crossAx val="200242304"/>
         <c:crosses val="autoZero"/>
@@ -937,8 +1161,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -965,7 +1192,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1000,7 +1233,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1019,9 +1258,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1059,7 +1298,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1093,6 +1332,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1127,9 +1367,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1302,650 +1543,683 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:J61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S40"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="9" width="8.7265625" style="12"/>
+    <col min="10" max="10" width="5.7265625" style="12" customWidth="1"/>
+    <col min="11" max="11" width="11.08984375" style="22" customWidth="1"/>
+    <col min="12" max="18" width="8.7265625" style="12"/>
+    <col min="19" max="19" width="15" style="12" customWidth="1"/>
+    <col min="20" max="16384" width="8.7265625" style="12"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
-      <c r="B2" s="12" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="12"/>
-    </row>
-    <row r="3" spans="2:10">
-      <c r="B3" t="s">
+      <c r="B1" s="11"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="1">
+      <c r="B2" s="13">
         <v>42104</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
-      <c r="B4" t="s">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C4">
+      <c r="B3" s="12">
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
-      <c r="B5" t="s">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="2">
+      <c r="B4" s="14">
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
-      <c r="B6" t="s">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="2">
+      <c r="B5" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
-      <c r="B8" s="12" t="s">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A7" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="12"/>
-    </row>
-    <row r="9" spans="2:10">
-      <c r="B9" t="s">
+      <c r="B7" s="11"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C9">
+      <c r="B8" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
-      <c r="B10" t="s">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A9" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="5">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10">
-      <c r="B12" s="12" t="s">
+      <c r="B9" s="17">
+        <v>10</v>
+      </c>
+      <c r="K9" s="23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-    </row>
-    <row r="13" spans="2:10">
-      <c r="B13" s="13">
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="K11" s="22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A12" s="18">
         <v>42104</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="B12" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-    </row>
-    <row r="14" spans="2:10">
-      <c r="B14" s="13">
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="K12" s="15">
         <v>42470</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="L12" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A13" s="18">
+        <v>42470</v>
+      </c>
+      <c r="B13" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-    </row>
-    <row r="15" spans="2:10">
-      <c r="B15" s="13">
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A14" s="18">
         <v>42835</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="B14" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-    </row>
-    <row r="16" spans="2:10">
-      <c r="B16" s="13">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="K14" s="22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A15" s="18">
         <v>43200</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="B15" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-    </row>
-    <row r="17" spans="2:10">
-      <c r="B17" s="13"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-    </row>
-    <row r="18" spans="2:10">
-      <c r="B18" s="13"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-    </row>
-    <row r="19" spans="2:10">
-      <c r="B19" s="13"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-    </row>
-    <row r="20" spans="2:10">
-      <c r="B20" s="13"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-    </row>
-    <row r="21" spans="2:10">
-      <c r="B21" s="13"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-    </row>
-    <row r="22" spans="2:10">
-      <c r="B22" s="13"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-    </row>
-    <row r="23" spans="2:10">
-      <c r="B23" s="13"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-    </row>
-    <row r="24" spans="2:10">
-      <c r="B24" s="13"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-    </row>
-    <row r="25" spans="2:10">
-      <c r="B25" s="13"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-    </row>
-    <row r="26" spans="2:10">
-      <c r="B26" s="13"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-    </row>
-    <row r="27" spans="2:10">
-      <c r="B27" s="13"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-    </row>
-    <row r="28" spans="2:10">
-      <c r="B28" s="13"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
-    </row>
-    <row r="30" spans="2:10">
-      <c r="B30" t="s">
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="K15" s="15">
+        <v>42104</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="16"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A16" s="18"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="K16" s="15">
+        <v>42134</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="16"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A17" s="18"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="K17" s="15">
+        <v>42165</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="16"/>
+      <c r="S17" s="16"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A18" s="18"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="K18" s="15">
+        <v>42195</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="16"/>
+      <c r="S18" s="16"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A19" s="18"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="K19" s="15">
+        <v>42226</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="16"/>
+      <c r="S19" s="16"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A20" s="18"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="K20" s="15">
+        <v>42257</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="16"/>
+      <c r="S20" s="16"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A21" s="18"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="K21" s="15">
+        <v>42287</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="M21" s="16"/>
+      <c r="N21" s="16"/>
+      <c r="O21" s="16"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="16"/>
+      <c r="R21" s="16"/>
+      <c r="S21" s="16"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A22" s="18"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="K22" s="15">
+        <v>42318</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="16"/>
+      <c r="P22" s="16"/>
+      <c r="Q22" s="16"/>
+      <c r="R22" s="16"/>
+      <c r="S22" s="16"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A23" s="18"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="K23" s="15">
+        <v>42348</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="M23" s="16"/>
+      <c r="N23" s="16"/>
+      <c r="O23" s="16"/>
+      <c r="P23" s="16"/>
+      <c r="Q23" s="16"/>
+      <c r="R23" s="16"/>
+      <c r="S23" s="16"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A24" s="18"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="K24" s="15">
+        <v>42379</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="M24" s="16"/>
+      <c r="N24" s="16"/>
+      <c r="O24" s="16"/>
+      <c r="P24" s="16"/>
+      <c r="Q24" s="16"/>
+      <c r="R24" s="16"/>
+      <c r="S24" s="16"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A25" s="18"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="K25" s="15">
+        <v>42410</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="M25" s="16"/>
+      <c r="N25" s="16"/>
+      <c r="O25" s="16"/>
+      <c r="P25" s="16"/>
+      <c r="Q25" s="16"/>
+      <c r="R25" s="16"/>
+      <c r="S25" s="16"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A26" s="18"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="K26" s="15">
+        <v>42439</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="M26" s="16"/>
+      <c r="N26" s="16"/>
+      <c r="O26" s="16"/>
+      <c r="P26" s="16"/>
+      <c r="Q26" s="16"/>
+      <c r="R26" s="16"/>
+      <c r="S26" s="16"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A27" s="18"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="K27" s="15">
+        <v>42470</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="M27" s="16"/>
+      <c r="N27" s="16"/>
+      <c r="O27" s="16"/>
+      <c r="P27" s="16"/>
+      <c r="Q27" s="16"/>
+      <c r="R27" s="16"/>
+      <c r="S27" s="16"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="K28" s="15">
+        <v>42470</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="16"/>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="16"/>
+      <c r="S28" s="16"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A29" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="K29" s="12"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A30" s="20" t="str">
+        <f t="array" ref="A30:B33">_xll.TestScript(B2,B3,B4,B5,A12:A27,B12:B27,B9,B8)</f>
+        <v>ALIVE</v>
+      </c>
+      <c r="B30" s="21">
+        <v>0.6</v>
+      </c>
+      <c r="K30" s="22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A31" s="20" t="str">
+        <v>AUTOCALL</v>
+      </c>
+      <c r="B31" s="21">
+        <v>84</v>
+      </c>
+      <c r="K31" s="15">
+        <v>42104</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="M31" s="16"/>
+      <c r="N31" s="16"/>
+      <c r="O31" s="16"/>
+      <c r="P31" s="16"/>
+      <c r="Q31" s="16"/>
+      <c r="R31" s="16"/>
+      <c r="S31" s="16"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A32" s="20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B32" s="21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K32" s="15">
+        <v>42470</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="M32" s="16"/>
+      <c r="N32" s="16"/>
+      <c r="O32" s="16"/>
+      <c r="P32" s="16"/>
+      <c r="Q32" s="16"/>
+      <c r="R32" s="16"/>
+      <c r="S32" s="16"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A33" s="20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B33" s="21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K33" s="15">
+        <v>42835</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="M33" s="16"/>
+      <c r="N33" s="16"/>
+      <c r="O33" s="16"/>
+      <c r="P33" s="16"/>
+      <c r="Q33" s="16"/>
+      <c r="R33" s="16"/>
+      <c r="S33" s="16"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="K34" s="15">
+        <v>43200</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="M34" s="16"/>
+      <c r="N34" s="16"/>
+      <c r="O34" s="16"/>
+      <c r="P34" s="16"/>
+      <c r="Q34" s="16"/>
+      <c r="R34" s="16"/>
+      <c r="S34" s="16"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="K35" s="12"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="K36" s="22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="K37" s="15">
+        <v>42104</v>
+      </c>
+      <c r="L37" s="16" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="31" spans="2:10">
-      <c r="B31" s="4" t="str">
-        <f t="array" aca="1" ref="B31:C34" ca="1">_xll.TestScript(C3,C4,C5,C6,B13:B28,C13:C28,C10,C9)</f>
-        <v>ALIVE</v>
-      </c>
-      <c r="C31" s="4">
-        <f ca="1"/>
-        <v>0.42542000000028468</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10">
-      <c r="B32" s="4" t="str">
-        <f ca="1"/>
-        <v>AUTOCALL</v>
-      </c>
-      <c r="C32" s="4">
-        <f ca="1"/>
-        <v>90.364399999974296</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10">
-      <c r="B33" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="C33" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10">
-      <c r="B34" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="C34" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10">
-      <c r="B36" t="s">
+      <c r="M37" s="16"/>
+      <c r="N37" s="16"/>
+      <c r="O37" s="16"/>
+      <c r="P37" s="16"/>
+      <c r="Q37" s="16"/>
+      <c r="R37" s="16"/>
+      <c r="S37" s="16"/>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="K38" s="15">
+        <v>42105</v>
+      </c>
+      <c r="L38" s="16" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="38" spans="2:10">
-      <c r="B38" t="s">
+      <c r="M38" s="16"/>
+      <c r="N38" s="16"/>
+      <c r="O38" s="16"/>
+      <c r="P38" s="16"/>
+      <c r="Q38" s="16"/>
+      <c r="R38" s="16"/>
+      <c r="S38" s="16"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="K39" s="15">
+        <v>42106</v>
+      </c>
+      <c r="L39" s="16" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="39" spans="2:10">
-      <c r="B39" s="13">
-        <v>42470</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14"/>
-    </row>
-    <row r="41" spans="2:10">
-      <c r="B41" t="s">
+      <c r="M39" s="16"/>
+      <c r="N39" s="16"/>
+      <c r="O39" s="16"/>
+      <c r="P39" s="16"/>
+      <c r="Q39" s="16"/>
+      <c r="R39" s="16"/>
+      <c r="S39" s="16"/>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="K40" s="15">
+        <v>42107</v>
+      </c>
+      <c r="L40" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C41">
-        <v>110</v>
-      </c>
-      <c r="D41" t="s">
-        <v>27</v>
-      </c>
-      <c r="E41">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10">
-      <c r="B42" s="13">
-        <v>42104</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="14"/>
-      <c r="J42" s="14"/>
-    </row>
-    <row r="43" spans="2:10">
-      <c r="B43" s="13">
-        <v>42134</v>
-      </c>
-      <c r="C43" s="14" t="str">
-        <f ca="1">"if spot() &gt; "&amp;$C$41&amp;" then alive = 0 endif"</f>
-        <v>if spot() &gt; 110 then alive = 0 endif</v>
-      </c>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="14"/>
-      <c r="J43" s="14"/>
-    </row>
-    <row r="44" spans="2:10">
-      <c r="B44" s="13">
-        <v>42165</v>
-      </c>
-      <c r="C44" s="14" t="str">
-        <f t="shared" ref="C44:C54" ca="1" si="0">"if spot() &gt; "&amp;$C$41&amp;" then alive = 0 endif"</f>
-        <v>if spot() &gt; 110 then alive = 0 endif</v>
-      </c>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="14"/>
-      <c r="J44" s="14"/>
-    </row>
-    <row r="45" spans="2:10">
-      <c r="B45" s="13">
-        <v>42195</v>
-      </c>
-      <c r="C45" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>if spot() &gt; 110 then alive = 0 endif</v>
-      </c>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="14"/>
-      <c r="J45" s="14"/>
-    </row>
-    <row r="46" spans="2:10">
-      <c r="B46" s="13">
-        <v>42226</v>
-      </c>
-      <c r="C46" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>if spot() &gt; 110 then alive = 0 endif</v>
-      </c>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="14"/>
-      <c r="J46" s="14"/>
-    </row>
-    <row r="47" spans="2:10">
-      <c r="B47" s="13">
-        <v>42257</v>
-      </c>
-      <c r="C47" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>if spot() &gt; 110 then alive = 0 endif</v>
-      </c>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="14"/>
-      <c r="J47" s="14"/>
-    </row>
-    <row r="48" spans="2:10">
-      <c r="B48" s="13">
-        <v>42287</v>
-      </c>
-      <c r="C48" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>if spot() &gt; 110 then alive = 0 endif</v>
-      </c>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14"/>
-      <c r="J48" s="14"/>
-    </row>
-    <row r="49" spans="2:10">
-      <c r="B49" s="13">
-        <v>42318</v>
-      </c>
-      <c r="C49" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>if spot() &gt; 110 then alive = 0 endif</v>
-      </c>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="14"/>
-      <c r="J49" s="14"/>
-    </row>
-    <row r="50" spans="2:10">
-      <c r="B50" s="13">
-        <v>42348</v>
-      </c>
-      <c r="C50" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>if spot() &gt; 110 then alive = 0 endif</v>
-      </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14"/>
-    </row>
-    <row r="51" spans="2:10">
-      <c r="B51" s="13">
-        <v>42379</v>
-      </c>
-      <c r="C51" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>if spot() &gt; 110 then alive = 0 endif</v>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14"/>
-    </row>
-    <row r="52" spans="2:10">
-      <c r="B52" s="13">
-        <v>42410</v>
-      </c>
-      <c r="C52" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>if spot() &gt; 110 then alive = 0 endif</v>
-      </c>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="14"/>
-      <c r="J52" s="14"/>
-    </row>
-    <row r="53" spans="2:10">
-      <c r="B53" s="13">
-        <v>42439</v>
-      </c>
-      <c r="C53" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>if spot() &gt; 110 then alive = 0 endif</v>
-      </c>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="14"/>
-      <c r="J53" s="14"/>
-    </row>
-    <row r="54" spans="2:10">
-      <c r="B54" s="13">
-        <v>42470</v>
-      </c>
-      <c r="C54" s="14" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>if spot() &gt; 110 then alive = 0 endif</v>
-      </c>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="14"/>
-      <c r="J54" s="14"/>
-    </row>
-    <row r="55" spans="2:10">
-      <c r="B55" s="13">
-        <f ca="1">B54</f>
-        <v>42470</v>
-      </c>
-      <c r="C55" s="14" t="str">
-        <f ca="1">"rko pays alive * max( spot() - "&amp;$E$41&amp;", 0)"</f>
-        <v>rko pays alive * max( spot() - 100, 0)</v>
-      </c>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="14"/>
-      <c r="J55" s="14"/>
-    </row>
-    <row r="57" spans="2:10">
-      <c r="B57" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10">
-      <c r="B58" s="13">
-        <v>42104</v>
-      </c>
-      <c r="C58" s="14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10">
-      <c r="B59" s="13">
-        <v>42470</v>
-      </c>
-      <c r="C59" s="14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="2:10">
-      <c r="B60" s="13">
-        <v>42835</v>
-      </c>
-      <c r="C60" s="14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10">
-      <c r="B61" s="13">
-        <v>43200</v>
-      </c>
-      <c r="C61" s="14" t="s">
-        <v>13</v>
-      </c>
+      <c r="M40" s="16"/>
+      <c r="N40" s="16"/>
+      <c r="O40" s="16"/>
+      <c r="P40" s="16"/>
+      <c r="Q40" s="16"/>
+      <c r="R40" s="16"/>
+      <c r="S40" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B12:J12"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A29:B29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:J33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
-      <c r="B2" s="12" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="12"/>
-    </row>
-    <row r="3" spans="2:10">
+      <c r="C2" s="10"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -1953,7 +2227,7 @@
         <v>42104</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>1</v>
       </c>
@@ -1961,7 +2235,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>2</v>
       </c>
@@ -1969,7 +2243,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>3</v>
       </c>
@@ -1977,97 +2251,97 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
-      <c r="B9" s="12" t="s">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-    </row>
-    <row r="10" spans="2:10">
-      <c r="B10" s="3">
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B10" s="1">
         <v>42104</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
-      <c r="B11" s="3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B11" s="1">
         <v>42470</v>
       </c>
       <c r="C11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
-      <c r="B12" s="3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B12" s="1">
         <v>42835</v>
       </c>
       <c r="C12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
-      <c r="B13" s="3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B13" s="1">
         <v>43200</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="2:5">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="9" t="b">
+      <c r="C18" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="D18" s="9" t="b">
-        <f ca="1">C18</f>
+      <c r="D18" s="8" t="b">
+        <f>C18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:5">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
         <v>1</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:5">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="6">
         <v>0</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="6">
         <v>1E-4</v>
       </c>
     </row>
-    <row r="21" spans="2:5">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="3">
         <v>0</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:5">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>14</v>
       </c>
@@ -2078,7 +2352,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="2:5">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>8</v>
       </c>
@@ -2086,174 +2360,174 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="2:5">
-      <c r="B24" s="5">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B24" s="4">
         <v>10000</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="3" t="e">
         <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B24,$B24,C$18,C$19),C$22,2)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="D24" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B24,$B24,D$18,D$19),D$22,2)</f>
         <v>90.223999999997403</v>
       </c>
-      <c r="D24" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B24,$B24,D$18,D$19),D$22,2)</f>
-        <v>90.223999999997403</v>
-      </c>
-      <c r="E24" s="4">
+      <c r="E24" s="3" t="e">
         <f ca="1">(D24-C24)/$D$20</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5">
-      <c r="B25" s="5">
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B25" s="4">
         <v>20000</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="3" t="e">
         <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B25,$B25,C$18,C$19),C$22,2)</f>
-        <v>90.457999999982079</v>
-      </c>
-      <c r="D25" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B25,$B25,D$18,D$19),D$22,2)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="D25" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B25,$B25,D$18,D$19),D$22,2)</f>
         <v>90.458499999982081</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="3" t="e">
         <f t="shared" ref="E25:E33" ca="1" si="0">(D25-C25)/$D$20</f>
-        <v>5.0000000000238742</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5">
-      <c r="B26" s="5">
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B26" s="4">
         <v>30000</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="3" t="e">
         <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B26,$B26,C$18,C$19),C$22,2)</f>
-        <v>90.362999999973212</v>
-      </c>
-      <c r="D26" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B26,$B26,D$18,D$19),D$22,2)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="D26" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B26,$B26,D$18,D$19),D$22,2)</f>
         <v>90.361999999973222</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="3" t="e">
         <f t="shared" ca="1" si="0"/>
-        <v>-9.9999999999056399</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5">
-      <c r="B27" s="5">
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B27" s="4">
         <v>40000</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="3" t="e">
         <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B27,$B27,C$18,C$19),C$22,2)</f>
-        <v>90.220750000007257</v>
-      </c>
-      <c r="D27" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B27,$B27,D$18,D$19),D$22,2)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="D27" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B27,$B27,D$18,D$19),D$22,2)</f>
         <v>90.219000000007256</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="3" t="e">
         <f t="shared" ca="1" si="0"/>
-        <v>-17.500000000012506</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5">
-      <c r="B28" s="5">
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B28" s="4">
         <v>50000</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="3" t="e">
         <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B28,$B28,C$18,C$19),C$22,2)</f>
-        <v>90.160200000033896</v>
-      </c>
-      <c r="D28" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B28,$B28,D$18,D$19),D$22,2)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="D28" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B28,$B28,D$18,D$19),D$22,2)</f>
         <v>90.157800000033887</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="3" t="e">
         <f t="shared" ca="1" si="0"/>
-        <v>-24.000000000086175</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5">
-      <c r="B29" s="5">
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B29" s="4">
         <v>60000</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="3" t="e">
         <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B29,$B29,C$18,C$19),C$22,2)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="D29" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B29,$B29,D$18,D$19),D$22,2)</f>
         <v>90.35516666665481</v>
       </c>
-      <c r="D29" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B29,$B29,D$18,D$19),D$22,2)</f>
-        <v>90.35516666665481</v>
-      </c>
-      <c r="E29" s="4">
+      <c r="E29" s="3" t="e">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5">
-      <c r="B30" s="5">
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B30" s="4">
         <v>70000</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="3" t="e">
         <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B30,$B30,C$18,C$19),C$22,2)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="D30" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B30,$B30,D$18,D$19),D$22,2)</f>
         <v>90.347142857107599</v>
       </c>
-      <c r="D30" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B30,$B30,D$18,D$19),D$22,2)</f>
-        <v>90.347142857107599</v>
-      </c>
-      <c r="E30" s="4">
+      <c r="E30" s="3" t="e">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5">
-      <c r="B31" s="5">
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B31" s="4">
         <v>80000</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="3" t="e">
         <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B31,$B31,C$18,C$19),C$22,2)</f>
-        <v>90.409624999958481</v>
-      </c>
-      <c r="D31" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B31,$B31,D$18,D$19),D$22,2)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="D31" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B31,$B31,D$18,D$19),D$22,2)</f>
         <v>90.40787499995848</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="3" t="e">
         <f t="shared" ca="1" si="0"/>
-        <v>-17.500000000012506</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5">
-      <c r="B32" s="5">
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B32" s="4">
         <v>90000</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="3" t="e">
         <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B32,$B32,C$18,C$19),C$22,2)</f>
-        <v>90.3547777778181</v>
-      </c>
-      <c r="D32" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B32,$B32,D$18,D$19),D$22,2)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="D32" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B32,$B32,D$18,D$19),D$22,2)</f>
         <v>90.353222222262531</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="3" t="e">
         <f t="shared" ca="1" si="0"/>
-        <v>-15.55555555569299</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5">
-      <c r="B33" s="5">
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B33" s="4">
         <v>100000</v>
       </c>
-      <c r="C33" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B33,$B33,C$18,C$19),C$22,2)</f>
+      <c r="C33" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B33,$B33,C$18,C$19),C$22,2)</f>
         <v>90.23189999997507</v>
       </c>
-      <c r="D33" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B33,$B33,D$18,D$19),D$22,2)</f>
+      <c r="D33" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B33,$B33,D$18,D$19),D$22,2)</f>
         <v>90.229899999975089</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="3" t="e">
         <f t="shared" ca="1" si="0"/>
-        <v>-19.99999999981128</v>
+        <v>#NAME?</v>
       </c>
     </row>
   </sheetData>
@@ -2267,21 +2541,21 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:J33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
-      <c r="B2" s="12" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="12"/>
-    </row>
-    <row r="3" spans="2:10">
+      <c r="C2" s="10"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -2289,7 +2563,7 @@
         <v>42104</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>1</v>
       </c>
@@ -2297,7 +2571,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>2</v>
       </c>
@@ -2305,7 +2579,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>3</v>
       </c>
@@ -2313,97 +2587,97 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
-      <c r="B9" s="12" t="s">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-    </row>
-    <row r="10" spans="2:10">
-      <c r="B10" s="3">
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B10" s="1">
         <v>42104</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
-      <c r="B11" s="3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B11" s="1">
         <v>42470</v>
       </c>
       <c r="C11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
-      <c r="B12" s="3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B12" s="1">
         <v>42835</v>
       </c>
       <c r="C12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
-      <c r="B13" s="3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B13" s="1">
         <v>43200</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="11" t="b">
+      <c r="C18" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="D18" s="10" t="b">
-        <f ca="1">C18</f>
+      <c r="D18" t="b">
+        <f>C18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
         <v>1</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="6">
         <v>0</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="6">
         <v>1E-4</v>
       </c>
     </row>
-    <row r="21" spans="2:7">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="3">
         <v>0</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>14</v>
       </c>
@@ -2414,7 +2688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>8</v>
       </c>
@@ -2428,254 +2702,254 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
-      <c r="B24" s="5">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B24" s="4">
         <v>10000</v>
       </c>
-      <c r="C24" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B24,$B24,C$18,C$19),C$22,2)</f>
-        <v>89.699999999997587</v>
-      </c>
-      <c r="D24" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B24,$B24,D$18,D$19),D$22,2)</f>
-        <v>89.699999999997587</v>
-      </c>
-      <c r="E24" s="4">
-        <f ca="1">(D24-C24)/$D$20</f>
+      <c r="C24" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B24,$B24,C$18,C$19),C$22,2)</f>
+        <v>90.223999999997403</v>
+      </c>
+      <c r="D24" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B24,$B24,D$18,D$19),D$22,2)</f>
+        <v>90.223999999997403</v>
+      </c>
+      <c r="E24" s="3">
+        <f>(D24-C24)/$D$20</f>
         <v>0</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="7" t="e">
         <f ca="1">Sharp!C24</f>
-        <v>89.699999999997587</v>
-      </c>
-      <c r="G24" s="8">
+        <v>#NAME?</v>
+      </c>
+      <c r="G24" s="7" t="e">
         <f ca="1">Sharp!E24</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B25" s="4">
+        <v>20000</v>
+      </c>
+      <c r="C25" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B25,$B25,C$18,C$19),C$22,2)</f>
+        <v>90.457999999982079</v>
+      </c>
+      <c r="D25" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B25,$B25,D$18,D$19),D$22,2)</f>
+        <v>90.458499999982081</v>
+      </c>
+      <c r="E25" s="3">
+        <f t="shared" ref="E25:E33" si="0">(D25-C25)/$D$20</f>
+        <v>5.0000000000238742</v>
+      </c>
+      <c r="F25" s="7" t="e">
+        <f ca="1">Sharp!C25</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G25" s="7" t="e">
+        <f ca="1">Sharp!E25</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B26" s="4">
+        <v>30000</v>
+      </c>
+      <c r="C26" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B26,$B26,C$18,C$19),C$22,2)</f>
+        <v>90.362999999973212</v>
+      </c>
+      <c r="D26" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B26,$B26,D$18,D$19),D$22,2)</f>
+        <v>90.361999999973222</v>
+      </c>
+      <c r="E26" s="3">
+        <f t="shared" si="0"/>
+        <v>-9.9999999999056399</v>
+      </c>
+      <c r="F26" s="7" t="e">
+        <f ca="1">Sharp!C26</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G26" s="7" t="e">
+        <f ca="1">Sharp!E26</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B27" s="4">
+        <v>40000</v>
+      </c>
+      <c r="C27" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B27,$B27,C$18,C$19),C$22,2)</f>
+        <v>90.220750000007257</v>
+      </c>
+      <c r="D27" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B27,$B27,D$18,D$19),D$22,2)</f>
+        <v>90.219000000007256</v>
+      </c>
+      <c r="E27" s="3">
+        <f t="shared" si="0"/>
+        <v>-17.500000000012506</v>
+      </c>
+      <c r="F27" s="7" t="e">
+        <f ca="1">Sharp!C27</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G27" s="7" t="e">
+        <f ca="1">Sharp!E27</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B28" s="4">
+        <v>50000</v>
+      </c>
+      <c r="C28" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B28,$B28,C$18,C$19),C$22,2)</f>
+        <v>90.160200000033896</v>
+      </c>
+      <c r="D28" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B28,$B28,D$18,D$19),D$22,2)</f>
+        <v>90.157800000033887</v>
+      </c>
+      <c r="E28" s="3">
+        <f t="shared" si="0"/>
+        <v>-24.000000000086175</v>
+      </c>
+      <c r="F28" s="7" t="e">
+        <f ca="1">Sharp!C28</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G28" s="7" t="e">
+        <f ca="1">Sharp!E28</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B29" s="4">
+        <v>60000</v>
+      </c>
+      <c r="C29" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B29,$B29,C$18,C$19),C$22,2)</f>
+        <v>90.35516666665481</v>
+      </c>
+      <c r="D29" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B29,$B29,D$18,D$19),D$22,2)</f>
+        <v>90.35516666665481</v>
+      </c>
+      <c r="E29" s="3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="2:7">
-      <c r="B25" s="5">
-        <v>20000</v>
-      </c>
-      <c r="C25" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B25,$B25,C$18,C$19),C$22,2)</f>
-        <v>90.056999999981969</v>
-      </c>
-      <c r="D25" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B25,$B25,D$18,D$19),D$22,2)</f>
-        <v>90.057499999981971</v>
-      </c>
-      <c r="E25" s="4">
-        <f t="shared" ref="E25:E33" ca="1" si="0">(D25-C25)/$D$20</f>
-        <v>5.0000000000238742</v>
-      </c>
-      <c r="F25" s="8">
-        <f ca="1">Sharp!C25</f>
-        <v>90.056999999981969</v>
-      </c>
-      <c r="G25" s="8">
-        <f ca="1">Sharp!E25</f>
-        <v>5.0000000000238742</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7">
-      <c r="B26" s="5">
-        <v>30000</v>
-      </c>
-      <c r="C26" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B26,$B26,C$18,C$19),C$22,2)</f>
-        <v>90.071999999973059</v>
-      </c>
-      <c r="D26" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B26,$B26,D$18,D$19),D$22,2)</f>
-        <v>90.071999999973059</v>
-      </c>
-      <c r="E26" s="4">
-        <f t="shared" ca="1" si="0"/>
+      <c r="F29" s="7" t="e">
+        <f ca="1">Sharp!C29</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G29" s="7" t="e">
+        <f ca="1">Sharp!E29</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B30" s="4">
+        <v>70000</v>
+      </c>
+      <c r="C30" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B30,$B30,C$18,C$19),C$22,2)</f>
+        <v>90.347142857107599</v>
+      </c>
+      <c r="D30" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B30,$B30,D$18,D$19),D$22,2)</f>
+        <v>90.347142857107599</v>
+      </c>
+      <c r="E30" s="3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F26" s="8">
-        <f ca="1">Sharp!C26</f>
-        <v>90.071999999973059</v>
-      </c>
-      <c r="G26" s="8">
-        <f ca="1">Sharp!E26</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7">
-      <c r="B27" s="5">
-        <v>40000</v>
-      </c>
-      <c r="C27" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B27,$B27,C$18,C$19),C$22,2)</f>
-        <v>90.558000000007993</v>
-      </c>
-      <c r="D27" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B27,$B27,D$18,D$19),D$22,2)</f>
-        <v>90.555250000007987</v>
-      </c>
-      <c r="E27" s="4">
-        <f t="shared" ca="1" si="0"/>
-        <v>-27.500000000060254</v>
-      </c>
-      <c r="F27" s="8">
-        <f ca="1">Sharp!C27</f>
-        <v>90.558000000007993</v>
-      </c>
-      <c r="G27" s="8">
-        <f ca="1">Sharp!E27</f>
-        <v>-27.500000000060254</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7">
-      <c r="B28" s="5">
-        <v>50000</v>
-      </c>
-      <c r="C28" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B28,$B28,C$18,C$19),C$22,2)</f>
-        <v>90.196400000035112</v>
-      </c>
-      <c r="D28" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B28,$B28,D$18,D$19),D$22,2)</f>
-        <v>90.193400000035112</v>
-      </c>
-      <c r="E28" s="4">
-        <f t="shared" ca="1" si="0"/>
-        <v>-30.000000000001137</v>
-      </c>
-      <c r="F28" s="8">
-        <f ca="1">Sharp!C28</f>
-        <v>90.196400000035112</v>
-      </c>
-      <c r="G28" s="8">
-        <f ca="1">Sharp!E28</f>
-        <v>-30.000000000001137</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7">
-      <c r="B29" s="5">
-        <v>60000</v>
-      </c>
-      <c r="C29" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B29,$B29,C$18,C$19),C$22,2)</f>
-        <v>90.404666666654421</v>
-      </c>
-      <c r="D29" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B29,$B29,D$18,D$19),D$22,2)</f>
-        <v>90.404999999987751</v>
-      </c>
-      <c r="E29" s="4">
-        <f t="shared" ca="1" si="0"/>
-        <v>3.33333333330188</v>
-      </c>
-      <c r="F29" s="8">
-        <f ca="1">Sharp!C29</f>
-        <v>90.404666666654421</v>
-      </c>
-      <c r="G29" s="8">
-        <f ca="1">Sharp!E29</f>
-        <v>3.33333333330188</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7">
-      <c r="B30" s="5">
-        <v>70000</v>
-      </c>
-      <c r="C30" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B30,$B30,C$18,C$19),C$22,2)</f>
-        <v>90.30714285710927</v>
-      </c>
-      <c r="D30" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B30,$B30,D$18,D$19),D$22,2)</f>
-        <v>90.305999999966403</v>
-      </c>
-      <c r="E30" s="4">
-        <f t="shared" ca="1" si="0"/>
-        <v>-11.428571428666601</v>
-      </c>
-      <c r="F30" s="8">
+      <c r="F30" s="7" t="e">
         <f ca="1">Sharp!C30</f>
-        <v>90.30714285710927</v>
-      </c>
-      <c r="G30" s="8">
+        <v>#NAME?</v>
+      </c>
+      <c r="G30" s="7" t="e">
         <f ca="1">Sharp!E30</f>
-        <v>-11.428571428666601</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7">
-      <c r="B31" s="5">
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B31" s="4">
         <v>80000</v>
       </c>
-      <c r="C31" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B31,$B31,C$18,C$19),C$22,2)</f>
-        <v>90.392749999958625</v>
-      </c>
-      <c r="D31" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B31,$B31,D$18,D$19),D$22,2)</f>
-        <v>90.392874999958622</v>
-      </c>
-      <c r="E31" s="4">
-        <f t="shared" ca="1" si="0"/>
-        <v>1.2499999999704414</v>
-      </c>
-      <c r="F31" s="8">
+      <c r="C31" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B31,$B31,C$18,C$19),C$22,2)</f>
+        <v>90.409624999958481</v>
+      </c>
+      <c r="D31" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B31,$B31,D$18,D$19),D$22,2)</f>
+        <v>90.40787499995848</v>
+      </c>
+      <c r="E31" s="3">
+        <f t="shared" si="0"/>
+        <v>-17.500000000012506</v>
+      </c>
+      <c r="F31" s="7" t="e">
         <f ca="1">Sharp!C31</f>
-        <v>90.392749999958625</v>
-      </c>
-      <c r="G31" s="8">
+        <v>#NAME?</v>
+      </c>
+      <c r="G31" s="7" t="e">
         <f ca="1">Sharp!E31</f>
-        <v>1.2499999999704414</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7">
-      <c r="B32" s="5">
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B32" s="4">
         <v>90000</v>
       </c>
-      <c r="C32" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B32,$B32,C$18,C$19),C$22,2)</f>
-        <v>90.341333333373967</v>
-      </c>
-      <c r="D32" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B32,$B32,D$18,D$19),D$22,2)</f>
-        <v>90.339000000040642</v>
-      </c>
-      <c r="E32" s="4">
-        <f t="shared" ca="1" si="0"/>
-        <v>-23.333333333255268</v>
-      </c>
-      <c r="F32" s="8">
+      <c r="C32" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B32,$B32,C$18,C$19),C$22,2)</f>
+        <v>90.3547777778181</v>
+      </c>
+      <c r="D32" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B32,$B32,D$18,D$19),D$22,2)</f>
+        <v>90.353222222262531</v>
+      </c>
+      <c r="E32" s="3">
+        <f t="shared" si="0"/>
+        <v>-15.55555555569299</v>
+      </c>
+      <c r="F32" s="7" t="e">
         <f ca="1">Sharp!C32</f>
-        <v>90.341333333373967</v>
-      </c>
-      <c r="G32" s="8">
+        <v>#NAME?</v>
+      </c>
+      <c r="G32" s="7" t="e">
         <f ca="1">Sharp!E32</f>
-        <v>-23.333333333255268</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="5">
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B33" s="4">
         <v>100000</v>
       </c>
-      <c r="C33" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B33,$B33,C$18,C$19),C$22,2)</f>
-        <v>90.409299999973271</v>
-      </c>
-      <c r="D33" s="4">
-        <f ca="1">INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B33,$B33,D$18,D$19),D$22,2)</f>
-        <v>90.40729999997329</v>
-      </c>
-      <c r="E33" s="4">
-        <f t="shared" ca="1" si="0"/>
+      <c r="C33" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+C$21,$C$5+C$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B33,$B33,C$18,C$19),C$22,2)</f>
+        <v>90.23189999997507</v>
+      </c>
+      <c r="D33" s="3">
+        <f>INDEX(_xll.TestScript($C$3,$C$4+D$21,$C$5+D$20,$C$6,$B$10:$B$16,$C$10:$C$16,$B33,$B33,D$18,D$19),D$22,2)</f>
+        <v>90.229899999975089</v>
+      </c>
+      <c r="E33" s="3">
+        <f t="shared" si="0"/>
         <v>-19.99999999981128</v>
       </c>
-      <c r="F33" s="8">
-        <f ca="1">Sharp!C33</f>
-        <v>90.409299999973271</v>
-      </c>
-      <c r="G33" s="8">
+      <c r="F33" s="7">
+        <f>Sharp!C33</f>
+        <v>90.23189999997507</v>
+      </c>
+      <c r="G33" s="7" t="e">
         <f ca="1">Sharp!E33</f>
-        <v>-19.99999999981128</v>
+        <v>#NAME?</v>
       </c>
     </row>
   </sheetData>
